--- a/12502900.xlsx
+++ b/12502900.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="3804" windowHeight="2808" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -194,13 +194,13 @@
     <t>Umuhan Ali Mohamud</t>
   </si>
   <si>
-    <t>CAP776</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>D2537</t>
   </si>
 </sst>
 </file>
@@ -907,7 +907,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1015,13 +1015,13 @@
         <v>450</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="M6" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N6" s="12" t="s">
         <v>49</v>

--- a/12502900.xlsx
+++ b/12502900.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -201,6 +201,18 @@
   </si>
   <si>
     <t>D2537</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Good</t>
   </si>
 </sst>
 </file>
@@ -1028,161 +1040,317 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>90</v>
+      </c>
+      <c r="E7" s="14">
+        <v>180</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>180</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>90</v>
+      </c>
+      <c r="E8" s="14">
+        <v>240</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>240</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="8">
+        <v>46243</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>180</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>180</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>240</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>180</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="8">
+        <v>46245</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>180</v>
+      </c>
+      <c r="F11" s="14">
+        <v>200</v>
+      </c>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>200</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>75</v>
+      </c>
+      <c r="E12" s="14">
+        <v>180</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>220</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>405</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>240</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="8">
+        <v>46248</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1204,7 +1372,9 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="8">
+        <v>46249</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1226,7 +1396,9 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="8">
+        <v>46250</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1248,7 +1420,9 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="8">
+        <v>46251</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1270,7 +1444,9 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="8">
+        <v>46252</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -1292,7 +1468,9 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="8">
+        <v>46253</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -1314,7 +1492,9 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="8">
+        <v>46254</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>

--- a/12502900.xlsx
+++ b/12502900.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -185,9 +185,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
-  </si>
-  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>D2537</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -213,6 +207,18 @@
   </si>
   <si>
     <t>Good</t>
+  </si>
+  <si>
+    <t>was feeling little down(unrelated to studies)</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>pg hunting</t>
+  </si>
+  <si>
+    <t>D1P2537</t>
   </si>
 </sst>
 </file>
@@ -832,7 +838,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -902,7 +908,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -919,7 +925,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -993,7 +999,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46240</v>
       </c>
@@ -1027,17 +1033,15 @@
         <v>450</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="M6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
@@ -1073,13 +1077,13 @@
         <v>480</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1117,13 +1121,13 @@
         <v>420</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1161,13 +1165,13 @@
         <v>420</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1205,13 +1209,13 @@
         <v>180</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1249,13 +1253,13 @@
         <v>410</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N11" s="17"/>
     </row>
@@ -1293,13 +1297,13 @@
         <v>405</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N12" s="17"/>
     </row>
@@ -1337,13 +1341,13 @@
         <v>330</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N13" s="17"/>
     </row>
@@ -1351,480 +1355,938 @@
       <c r="A14" s="8">
         <v>46248</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>430</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>75</v>
+      </c>
+      <c r="E14" s="14">
+        <v>240</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>280</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>355</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46249</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>45</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>240</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>310</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>275</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46250</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>400</v>
+      </c>
+      <c r="C16" s="14">
+        <v>45</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>280</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>330</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>265</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>46251</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>180</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>200</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46252</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>200</v>
+      </c>
+      <c r="F18" s="14">
+        <v>200</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>240</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46253</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
+        <v>180</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>240</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46254</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <v>210</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>60</v>
+      </c>
+      <c r="E21" s="14">
+        <v>230</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>320</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B22" s="14">
+        <v>400</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>230</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>45</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>320</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>390</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>165</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>90</v>
+      </c>
+      <c r="E24" s="14">
+        <v>210</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>240</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>320</v>
+      </c>
+      <c r="F25" s="14">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>320</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>180</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1225</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>215</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>180</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>180</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>320</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>90</v>
+      </c>
+      <c r="E29" s="14">
+        <v>300</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>210</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <v>360</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>380</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>280</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>90</v>
+      </c>
+      <c r="E32" s="14">
+        <v>185</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>200</v>
+      </c>
+      <c r="F33" s="14">
+        <v>100</v>
+      </c>
+      <c r="G33" s="14">
+        <v>2</v>
+      </c>
+      <c r="H33" s="14">
+        <v>380</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>100</v>
+      </c>
+      <c r="E34" s="14">
+        <v>240</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>210</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="8">
+        <v>46269</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
